--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2331-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2331-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{01A70992-F928-4654-AD0C-734EAF5D582E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D812151-9905-4D8A-97D2-E89D82B003F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{FBFD1A96-AC42-46E7-B5BF-410ADEEFE487}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{82FAEFF5-CD5F-4DCA-AACF-08782C178774}"/>
   </bookViews>
   <sheets>
     <sheet name="2331-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1475,21 +1475,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{956C1D52-5E28-461E-B796-2EAC23C73231}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ABFFAA6-406D-45F6-B43A-29DEED44C1F0}">
   <dimension ref="A1:R54"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1517,7 +1517,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1547,7 +1547,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1593,7 +1593,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1643,7 +1643,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1697,7 +1697,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1753,7 +1753,7 @@
         <v>1.1499999999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1809,7 +1809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1863,7 +1863,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1919,7 +1919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>3.28</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2141,7 +2141,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>25</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2022</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>25</v>
       </c>
@@ -2363,7 +2363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>25</v>
       </c>
@@ -2419,7 +2419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>2021</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>25</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>25</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>4.28</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="39">
         <v>2020</v>
       </c>
@@ -2639,7 +2639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2019</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>25</v>
       </c>
@@ -2861,7 +2861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -2917,7 +2917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2018</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>5.57</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2017</v>
       </c>
@@ -3025,7 +3025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2016</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>11.8</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>2015</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>16.399999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2014</v>
       </c>
@@ -3187,7 +3187,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2013</v>
       </c>
@@ -3241,7 +3241,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2012</v>
       </c>
@@ -3295,7 +3295,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2011</v>
       </c>
@@ -3349,7 +3349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2010</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>2009</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2008</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>8.48</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <v>2007</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2006</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>2005</v>
       </c>
@@ -3673,7 +3673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2004</v>
       </c>
@@ -3727,7 +3727,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>2003</v>
       </c>
@@ -3781,7 +3781,7 @@
         <v>7.92</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39">
         <v>2002</v>
       </c>
@@ -3835,7 +3835,7 @@
         <v>3.55</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
         <v>2001</v>
       </c>
@@ -3889,7 +3889,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="39">
         <v>2000</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
         <v>1999</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="39">
         <v>1998</v>
       </c>
@@ -4051,7 +4051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>1997</v>
       </c>
@@ -4105,7 +4105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="39">
         <v>1996</v>
       </c>
@@ -4159,7 +4159,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="37">
         <v>1995</v>
       </c>
@@ -4213,7 +4213,7 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="39">
         <v>1994</v>
       </c>
@@ -4267,7 +4267,7 @@
         <v>4.05</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="37">
         <v>1993</v>
       </c>
@@ -4321,7 +4321,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="39" t="s">
         <v>44</v>
       </c>
